--- a/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_404_R46.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_404_R46.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.0062</v>
+        <v>6.2391</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3079</v>
+        <v>1.2842</v>
       </c>
       <c r="F2" t="n">
-        <v>5.6983</v>
+        <v>4.9549</v>
       </c>
       <c r="G2" t="n">
         <v>2.6709</v>
@@ -610,13 +610,13 @@
         <v>1.1374</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3353</v>
+        <v>1.5682</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1855</v>
+        <v>0.1618</v>
       </c>
       <c r="U2" t="n">
-        <v>2.1498</v>
+        <v>1.4064</v>
       </c>
       <c r="V2" t="n">
         <v>1.0901</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9198</v>
+        <v>5.5807</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5153</v>
+        <v>5.9823</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5956</v>
+        <v>-0.4016</v>
       </c>
       <c r="G3" t="n">
         <v>6.455</v>
@@ -688,13 +688,13 @@
         <v>0.6824</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2658</v>
+        <v>0.395</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4908</v>
+        <v>-0.0238</v>
       </c>
       <c r="U3" t="n">
-        <v>0.225</v>
+        <v>0.4189</v>
       </c>
       <c r="V3" t="n">
         <v>-1.9519</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1509</v>
+        <v>3.3412</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1397</v>
+        <v>0.3092</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2906</v>
+        <v>3.032</v>
       </c>
       <c r="G4" t="n">
         <v>2.0184</v>
@@ -766,13 +766,13 @@
         <v>1.3648</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0049</v>
+        <v>0.1855</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.221</v>
+        <v>-0.7721</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2162</v>
+        <v>0.9576</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9269</v>
+        <v>2.498</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.583</v>
+        <v>-0.0442</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5099</v>
+        <v>2.5422</v>
       </c>
       <c r="G5" t="n">
         <v>0.8013</v>
@@ -844,13 +844,13 @@
         <v>0.9099</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0574</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8499</v>
+        <v>-0.3112</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9073</v>
+        <v>0.9396</v>
       </c>
       <c r="V5" t="n">
         <v>0.1583</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7928</v>
+        <v>1.8646</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07630000000000001</v>
+        <v>-0.0135</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7165</v>
+        <v>1.8781</v>
       </c>
       <c r="G6" t="n">
         <v>0.5557</v>
@@ -922,13 +922,13 @@
         <v>1.1374</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2634</v>
+        <v>0.3352</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0837</v>
+        <v>-0.1735</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3471</v>
+        <v>0.5087</v>
       </c>
       <c r="V6" t="n">
         <v>2.3386</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. WARD</t>
+          <t>T. WALKUP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6178</v>
+        <v>1.2244</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2613</v>
+        <v>-0.7873</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3564</v>
+        <v>2.0118</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6222</v>
+        <v>2.8561</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1943</v>
+        <v>1.4353</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8164</v>
+        <v>1.4207</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3839</v>
+        <v>2.3971</v>
       </c>
       <c r="K7" t="n">
-        <v>0.374</v>
+        <v>1.7598</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0099</v>
+        <v>0.6374</v>
       </c>
       <c r="M7" t="n">
-        <v>1.2383</v>
+        <v>0.4589</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5682</v>
+        <v>-0.3244</v>
       </c>
       <c r="O7" t="n">
-        <v>1.8065</v>
+        <v>0.7834</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5923</v>
+        <v>-1.1374</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2747</v>
+        <v>-2.5022</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6824</v>
+        <v>1.3648</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9746</v>
+        <v>0.7542</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9939</v>
+        <v>-0.6823</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0192</v>
+        <v>1.4365</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3867</v>
+        <v>-1.2485</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1583</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5451</v>
+        <v>-1.2485</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. WALKUP</t>
+          <t>T. WARD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6785</v>
+        <v>1.0592</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3979</v>
+        <v>-0.5558</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0764</v>
+        <v>1.615</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8561</v>
+        <v>2.6222</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4353</v>
+        <v>-0.1943</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4207</v>
+        <v>2.8164</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3971</v>
+        <v>1.3839</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7598</v>
+        <v>0.374</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6374</v>
+        <v>1.0099</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4589</v>
+        <v>1.2383</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3244</v>
+        <v>-0.5682</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7834</v>
+        <v>1.8065</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1374</v>
+        <v>-1.5923</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.5022</v>
+        <v>-2.2747</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3648</v>
+        <v>0.6824</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2082</v>
+        <v>0.416</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2929</v>
+        <v>0.1767</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5011</v>
+        <v>0.2393</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2485</v>
+        <v>-0.3867</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1583</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2485</v>
+        <v>-0.5451</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2903</v>
+        <v>0.7967</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3328</v>
+        <v>-1.9557</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6231</v>
+        <v>2.7524</v>
       </c>
       <c r="G9" t="n">
         <v>0.5992</v>
@@ -1156,13 +1156,13 @@
         <v>1.3648</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3089</v>
+        <v>0.1975</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7901</v>
+        <v>-0.413</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4812</v>
+        <v>0.6105</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. JONES</t>
+          <t>C. JOSEPH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.089</v>
+        <v>0.2902</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9525</v>
+        <v>-0.6939</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8635</v>
+        <v>0.9841</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3578</v>
+        <v>0.1193</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3098</v>
+        <v>0.1913</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.048</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1435</v>
+        <v>-0.5802</v>
       </c>
       <c r="K10" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0863</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0745</v>
+        <v>-0.6665</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5013</v>
+        <v>0.6995</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3788</v>
+        <v>0.105</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1225</v>
+        <v>0.5945</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2275</v>
+        <v>0.6824</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1374</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9099</v>
+        <v>0.6824</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1796</v>
+        <v>-0.3532</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2753</v>
+        <v>-0.1137</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4549</v>
+        <v>-0.2395</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3167</v>
+        <v>-0.1583</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3167</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.1583</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. JOSEPH</t>
+          <t>T. JONES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3383</v>
+        <v>-0.062</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9992</v>
+        <v>-0.7639</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6609</v>
+        <v>0.7019</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1193</v>
+        <v>-0.3578</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1913</v>
+        <v>-0.3098</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.048</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5802</v>
+        <v>0.1435</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0863</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6665</v>
+        <v>0.0745</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6995</v>
+        <v>-0.5013</v>
       </c>
       <c r="N11" t="n">
-        <v>0.105</v>
+        <v>-0.3788</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5945</v>
+        <v>-0.1225</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6824</v>
+        <v>-0.2275</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1374</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6824</v>
+        <v>0.9099</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9817</v>
+        <v>0.2065</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.419</v>
+        <v>-0.0867</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5628</v>
+        <v>0.2933</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1583</v>
+        <v>0.3167</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.3167</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0971</v>
+        <v>-0.9284</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.383</v>
+        <v>-0.3111</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.6172</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8054</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4501</v>
+        <v>-0.2813</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3591</v>
+        <v>-0.2873</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.091</v>
+        <v>0.006</v>
       </c>
       <c r="V12" t="n">
         <v>0.1583</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.2265</v>
+        <v>-2.1942</v>
       </c>
       <c r="E13" t="n">
         <v>-1.0235</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.203</v>
+        <v>-1.1707</v>
       </c>
       <c r="G13" t="n">
         <v>-0.7141</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1939</v>
+        <v>-0.1616</v>
       </c>
       <c r="T13" t="n">
         <v>-0.2873</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0934</v>
+        <v>0.1257</v>
       </c>
       <c r="V13" t="n">
         <v>-1.3185</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>18.6323</v>
+        <v>19.7095</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3492</v>
+        <v>1.4268</v>
       </c>
       <c r="F14" t="n">
-        <v>18.2828</v>
+        <v>18.2829</v>
       </c>
       <c r="G14" t="n">
         <v>16.8208</v>
@@ -1528,7 +1528,7 @@
         <v>8.037100000000002</v>
       </c>
       <c r="M14" t="n">
-        <v>5.792300000000001</v>
+        <v>5.792300000000002</v>
       </c>
       <c r="N14" t="n">
         <v>-1.0971</v>
@@ -1537,7 +1537,7 @@
         <v>6.8895</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.33066907387547e-16</v>
+        <v>-3.05311331771918e-16</v>
       </c>
       <c r="Q14" t="n">
         <v>-10.2363</v>
@@ -1546,13 +1546,13 @@
         <v>10.2362</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8132</v>
+        <v>3.8905</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.8897</v>
+        <v>-2.8124</v>
       </c>
       <c r="U14" t="n">
-        <v>6.703</v>
+        <v>6.703000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-1.0019</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. BIBEROVIC</t>
+          <t>T. HORTON TUCKER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,40 +1579,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6981</v>
+        <v>1.9536</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1376</v>
+        <v>0.1835</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5605</v>
+        <v>1.7701</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1907</v>
+        <v>-1.6397</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3142</v>
+        <v>1.6769</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1235</v>
+        <v>-3.3166</v>
       </c>
       <c r="J15" t="n">
-        <v>2.55</v>
+        <v>-0.9916</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1886</v>
+        <v>1.7407</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3614</v>
+        <v>-2.7323</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3594</v>
+        <v>-0.6481</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1256</v>
+        <v>-0.0638</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.485</v>
+        <v>-0.5843</v>
       </c>
       <c r="P15" t="n">
         <v>0.4549</v>
@@ -1624,28 +1624,28 @@
         <v>1.5923</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6657999999999999</v>
+        <v>-0.2903</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1799</v>
+        <v>-1.1162</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4859</v>
+        <v>0.8259</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3867</v>
+        <v>3.4287</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5451</v>
+        <v>3.4287</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. HORTON TUCKER</t>
+          <t>T. BIBEROVIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0045</v>
+        <v>1.8289</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0668</v>
+        <v>1.2037</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9377</v>
+        <v>0.6252</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.6397</v>
+        <v>1.1907</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6769</v>
+        <v>1.3142</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.3166</v>
+        <v>-0.1235</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.9916</v>
+        <v>2.55</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7407</v>
+        <v>1.1886</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.7323</v>
+        <v>1.3614</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6481</v>
+        <v>-1.3594</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0638</v>
+        <v>0.1256</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5843</v>
+        <v>-1.485</v>
       </c>
       <c r="P16" t="n">
         <v>0.4549</v>
@@ -1702,28 +1702,28 @@
         <v>1.5923</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2395</v>
+        <v>-0.2034</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2329</v>
+        <v>-0.754</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9933999999999999</v>
+        <v>0.5505</v>
       </c>
       <c r="V16" t="n">
-        <v>3.4287</v>
+        <v>0.3867</v>
       </c>
       <c r="W16" t="n">
-        <v>3.4287</v>
+        <v>0.5451</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1583</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. BIRCH</t>
+          <t>N. DE COLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3858</v>
+        <v>1.1483</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0189</v>
+        <v>0.6071</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4046</v>
+        <v>0.5413</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1834</v>
+        <v>0.6419</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2595</v>
+        <v>-0.9493</v>
       </c>
       <c r="I17" t="n">
-        <v>0.443</v>
+        <v>1.5912</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1716</v>
+        <v>1.3163</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2089</v>
+        <v>-0.3642</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0373</v>
+        <v>1.6804</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3551</v>
+        <v>-0.6744</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0506</v>
+        <v>-0.5851</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4057</v>
+        <v>-0.0893</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9099</v>
+        <v>1.3648</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1374</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2275</v>
+        <v>1.3648</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1805</v>
+        <v>-0.5417</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1318</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0487</v>
+        <v>0.1675</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9318</v>
+        <v>-0.3167</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1583</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.7734</v>
+        <v>-0.3167</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. DE COLO</t>
+          <t>K. BIRCH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3061</v>
+        <v>0.777</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0234</v>
+        <v>-1.3691</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2827</v>
+        <v>2.146</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6419</v>
+        <v>0.1834</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9493</v>
+        <v>-0.2595</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5912</v>
+        <v>0.443</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3163</v>
+        <v>-0.1716</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3642</v>
+        <v>-0.2089</v>
       </c>
       <c r="L18" t="n">
-        <v>1.6804</v>
+        <v>0.0373</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6744</v>
+        <v>0.3551</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5851</v>
+        <v>-0.0506</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0893</v>
+        <v>0.4057</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3648</v>
+        <v>-0.9099</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1374</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3648</v>
+        <v>0.2275</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3839</v>
+        <v>0.5717</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2929</v>
+        <v>-0.2184</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0911</v>
+        <v>0.7901</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3167</v>
+        <v>0.9318</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.1583</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3167</v>
+        <v>0.7734</v>
       </c>
     </row>
     <row r="19">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9241</v>
+        <v>-0.9367</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.031</v>
+        <v>-0.9143</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1069</v>
+        <v>-0.0224</v>
       </c>
       <c r="G20" t="n">
         <v>-1.8232</v>
@@ -2014,13 +2014,13 @@
         <v>0.4549</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0575</v>
+        <v>0.0449</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2873</v>
+        <v>-0.1706</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3448</v>
+        <v>0.2155</v>
       </c>
       <c r="V20" t="n">
         <v>0.3867</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4111</v>
+        <v>-2.6643</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.99</v>
+        <v>-2.3402</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4212</v>
+        <v>-0.3242</v>
       </c>
       <c r="G21" t="n">
         <v>-2.1526</v>
@@ -2092,13 +2092,13 @@
         <v>0.6824</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1964</v>
+        <v>-0.0568</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1318</v>
+        <v>-0.2184</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0646</v>
+        <v>0.1616</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1289</v>
+        <v>-2.9534</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1787</v>
+        <v>-0.062</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9501</v>
+        <v>-2.8914</v>
       </c>
       <c r="G22" t="n">
         <v>-0.512</v>
@@ -2170,13 +2170,13 @@
         <v>1.5923</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6632</v>
+        <v>-0.4878</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0174</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3542</v>
+        <v>0.4129</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4086</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4748</v>
+        <v>-3.775</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.6135</v>
+        <v>-4.2633</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1388</v>
+        <v>0.4884</v>
       </c>
       <c r="G23" t="n">
         <v>-4.5634</v>
@@ -2248,13 +2248,13 @@
         <v>0.2275</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9123</v>
+        <v>-0.2125</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6464</v>
+        <v>-0.2962</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2658</v>
+        <v>0.0837</v>
       </c>
       <c r="V23" t="n">
         <v>0.7734</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.6998</v>
+        <v>-4.9928</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.0322</v>
+        <v>-4.4485</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6676</v>
+        <v>-0.5442</v>
       </c>
       <c r="G24" t="n">
         <v>-2.8402</v>
@@ -2326,13 +2326,13 @@
         <v>1.8198</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3146</v>
+        <v>-0.6076</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.0111</v>
+        <v>-1.4275</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6966</v>
+        <v>0.8199</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0901</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.5435</v>
+        <v>-8.395099999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.6462</v>
+        <v>-6.8797</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8974</v>
+        <v>-1.5155</v>
       </c>
       <c r="G25" t="n">
         <v>-5.4613</v>
@@ -2404,13 +2404,13 @@
         <v>0.6824</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3998</v>
+        <v>-0.2514</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6583</v>
+        <v>-0.8918</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2585</v>
+        <v>0.6404</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0901</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-18.6321</v>
+        <v>-17.8539</v>
       </c>
       <c r="E26" t="n">
-        <v>-18.2827</v>
+        <v>-18.2828</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.3495000000000004</v>
+        <v>0.4288999999999994</v>
       </c>
       <c r="G26" t="n">
         <v>-16.8208</v>
@@ -2482,13 +2482,13 @@
         <v>10.2362</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.813099999999999</v>
+        <v>-2.0349</v>
       </c>
       <c r="T26" t="n">
-        <v>-6.7028</v>
+        <v>-6.703</v>
       </c>
       <c r="U26" t="n">
-        <v>3.8898</v>
+        <v>4.667999999999999</v>
       </c>
       <c r="V26" t="n">
         <v>1.0018</v>
